--- a/ESE_Cash_Flow_Model_v2.xlsx
+++ b/ESE_Cash_Flow_Model_v2.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,8 +78,24 @@
       <color rgb="00C8960C"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001B3A5C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -98,8 +114,14 @@
         <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B3A5C"/>
+        <bgColor rgb="001B3A5C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -121,11 +143,25 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -165,6 +201,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -530,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1256,6 +1301,312 @@
       <c r="B38" s="11" t="inlineStr">
         <is>
           <t>~3.6M EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>Capital Equipment — Self-Host Scenario (REFERENCE ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>Not in base case. Hardware purchase decision deferred to Y3+ Board approval. All prices Egypt landed (30-50% customs). 1 USD ≈ 52 EGP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="21" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B44" s="21" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>Capital Cost (one-time)</t>
+        </is>
+      </c>
+      <c r="D44" s="21" t="inlineStr">
+        <is>
+          <t>Monthly Opex</t>
+        </is>
+      </c>
+      <c r="E44" s="21" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F44" s="21" t="inlineStr">
+        <is>
+          <t>Break-even vs Cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>GLM 5.1 INT4, 8× A100 80GB, Dell XE9680</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>10.4M – 14.6M EGP</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="inlineStr">
+        <is>
+          <t>40-60K/mo</t>
+        </is>
+      </c>
+      <c r="E45" s="22" t="inlineStr">
+        <is>
+          <t>20-30 users</t>
+        </is>
+      </c>
+      <c r="F45" s="22" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>GLM 5.1 FP8, 8× H200 141GB, Dell XE9680</t>
+        </is>
+      </c>
+      <c r="C46" s="22" t="inlineStr">
+        <is>
+          <t>18.2M – 23.4M EGP</t>
+        </is>
+      </c>
+      <c r="D46" s="22" t="inlineStr">
+        <is>
+          <t>60-80K/mo</t>
+        </is>
+      </c>
+      <c r="E46" s="22" t="inlineStr">
+        <is>
+          <t>30-40 users</t>
+        </is>
+      </c>
+      <c r="F46" s="22" t="inlineStr">
+        <is>
+          <t>2-3 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>Individual GPU Pricing (Egyptian Market, April 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="21" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="inlineStr">
+        <is>
+          <t>VRAM</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="inlineStr">
+        <is>
+          <t>USD Each</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="inlineStr">
+        <is>
+          <t>EGP Each (landed)</t>
+        </is>
+      </c>
+      <c r="E50" s="21" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>NVIDIA A100 80GB PCIe</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>80 GB</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>$15K-17K</t>
+        </is>
+      </c>
+      <c r="D51" s="22" t="inlineStr">
+        <is>
+          <t>~1,135,000</t>
+        </is>
+      </c>
+      <c r="E51" s="22" t="inlineStr">
+        <is>
+          <t>ServerBasket Egypt</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>NVIDIA H100 80GB SXM5</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>80 GB</t>
+        </is>
+      </c>
+      <c r="C52" s="22" t="inlineStr">
+        <is>
+          <t>$35K-40K</t>
+        </is>
+      </c>
+      <c r="D52" s="22" t="inlineStr">
+        <is>
+          <t>~1.8M-2.1M</t>
+        </is>
+      </c>
+      <c r="E52" s="22" t="inlineStr">
+        <is>
+          <t>OEM (in-server)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t>NVIDIA H200 141GB SXM5</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>141 GB</t>
+        </is>
+      </c>
+      <c r="C53" s="22" t="inlineStr">
+        <is>
+          <t>$35K-45K</t>
+        </is>
+      </c>
+      <c r="D53" s="22" t="inlineStr">
+        <is>
+          <t>~1.8M-2.3M</t>
+        </is>
+      </c>
+      <c r="E53" s="22" t="inlineStr">
+        <is>
+          <t>OEM (in-server)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>NVIDIA RTX 4090 24GB</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>24 GB</t>
+        </is>
+      </c>
+      <c r="C54" s="22" t="inlineStr">
+        <is>
+          <t>$2.1K-3K</t>
+        </is>
+      </c>
+      <c r="D54" s="22" t="inlineStr">
+        <is>
+          <t>110K-155K</t>
+        </is>
+      </c>
+      <c r="E54" s="22" t="inlineStr">
+        <is>
+          <t>Baraka / Compumarts</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>NVIDIA RTX 5090 32GB</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>32 GB</t>
+        </is>
+      </c>
+      <c r="C55" s="22" t="inlineStr">
+        <is>
+          <t>$3K-3.85K</t>
+        </is>
+      </c>
+      <c r="D55" s="22" t="inlineStr">
+        <is>
+          <t>157K-200K</t>
+        </is>
+      </c>
+      <c r="E55" s="22" t="inlineStr">
+        <is>
+          <t>Compumarts / Baraka</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>Dell PowerEdge T560</t>
+        </is>
+      </c>
+      <c r="B56" s="22" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="C56" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D56" s="22" t="inlineStr">
+        <is>
+          <t>~120K-180K</t>
+        </is>
+      </c>
+      <c r="E56" s="22" t="inlineStr">
+        <is>
+          <t>Elite Technology</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1795,6 +2146,107 @@
       <c r="A27" s="12" t="inlineStr">
         <is>
           <t>⚠ Model B is cash-negative through Y3. Strategic market-entry investment — real return in Y4+ (Model C at 10× ticket size).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>Capital Equipment Reference — Self-Host Scenario (for management Q&amp;A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>Model B stays cloud-first. Hardware purchase NOT in base case. See Model A sheet for full 3-tier breakdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>Capital Cost</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>Monthly Opex</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>Break-even vs Cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2 — 8× A100 80GB (GLM 5.1 INT4)</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>10.4M – 14.6M EGP</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>40-60K/mo</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>3-5 yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>Tier 1 — 8× H200 141GB (GLM 5.1 FP8)</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>18.2M – 23.4M EGP</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>60-80K/mo</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>2-3 yr → buy wins</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>Cloud vs. Buy Verdict for Model B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>Tier 3 (5.2-7.3M) ÷ 1.8M/yr TAM = 3-4 years just to recover hardware. Cloud API at ~1.2M/yr is cheaper through Y5+.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>Self-host only at Model C scale (8M+ per deal, customer pays hardware). Hardware will be 30-50% cheaper by Y4.</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2711,6 +3163,97 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>Hardware Capital Costs (Reference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>Tier 3 — Qwen3-32B 4× A100 80GB</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>5.2M – 7.3M EGP one-time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>Tier 2 — GLM 5.1 INT4 8× A100 80GB</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>10.4M – 14.6M EGP one-time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>Tier 1 — GLM 5.1 FP8 8× H200 141GB</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>18.2M – 23.4M EGP one-time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>Egypt GPU Import Markup</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>30-50% above international MSRP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>Hardware Purchase Trigger</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>Only at Model C scale (8M+ per deal, customer-funded)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>AI Depreciation Assumption</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>-40% hardware cost per 2 years (same capability gets cheaper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>Self-Host Decision Gate</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>Y3Q4 Board review — not before</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>

--- a/ESE_Cash_Flow_Model_v2.xlsx
+++ b/ESE_Cash_Flow_Model_v2.xlsx
@@ -121,7 +121,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -157,11 +157,99 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -210,6 +298,10 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -575,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -945,17 +1037,17 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Claude API</t>
+          <t>Hardware capex share (25% of 5,500K)</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>80K</t>
+          <t>1,375K</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -965,129 +1057,133 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Migrate to RunPod Y2Q2</t>
+          <t>One-time, EGPC-mandated, Egypt landed</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Self-hosted Qwen3-32B (RunPod)</t>
+          <t>Colocation share (25% of 420K/yr)</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>105K</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>540K</t>
+          <t>105K</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>720K</t>
+          <t>105K</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>From Y2Q2</t>
+          <t>Data center + electricity</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>480K</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>800K</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>1,200K</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DevOps/ML Engineer share (25%)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>45K</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>90K</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>90K</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Shared hire, Model B pays 75%</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Certifications + Legal</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>400K</t>
+          <t>480K</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>150K</t>
+          <t>800K</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>100K</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>Y1 heavier</t>
-        </is>
-      </c>
+          <t>1,200K</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Payment Gateway (~3%)</t>
+          <t>Certifications + Legal</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>20K</t>
+          <t>400K</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>130K</t>
+          <t>150K</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>265K</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr"/>
+          <t>100K</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Y1 heavier</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Customer Support Tools</t>
+          <t>Payment Gateway (~3%)</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>30K</t>
+          <t>20K</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>50K</t>
+          <t>130K</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>80K</t>
+          <t>265K</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr"/>
@@ -1095,390 +1191,405 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
+          <t>Customer Support Tools</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>30K</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>50K</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>80K</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
           <t>Misc / Contingency (10%)</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>260K</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>390K</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>480K</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>2,830K</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>4,280K</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>5,325K</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>4,275K</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>3,735K</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>4,800K</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Net Cash Flow Summary</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr"/>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr"/>
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>3-Yr Cumulative</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>650K</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>4,300K</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>8,800K</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>13,750K</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>650K</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>4,300K</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>8,800K</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>13,750K</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>Costs</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>(2,830K)</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>(4,280K)</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>(5,325K)</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>(12,435K)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>(4,275K)</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>(3,735K)</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>(4,800K)</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>(12,810K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>(2,180K)</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>+20K</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>+3,475K</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>+1,315K</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>(3,625K)</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>+565K</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>+4,000K</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>+940K</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Key Metrics</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>Break-even</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>Y2Q4 (Month ~22)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>3-Year ROI</t>
+          <t>Break-even</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>~37%</t>
+          <t>Y2Q4 (Month ~22)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>IRR (quarterly)</t>
+          <t>Break-even</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>~22-28%</t>
+          <t>Y2Q4 (Month ~22)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
+          <t>3-Year ROI</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>~18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>IRR (quarterly)</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>~10-15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Cumulative Investment</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>~3.6M EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="19" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>~5.1M EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>Capital Equipment — Self-Host Scenario (REFERENCE ONLY)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>Not in base case. Hardware purchase decision deferred to Y3+ Board approval. All prices Egypt landed (30-50% customs). 1 USD ≈ 52 EGP.</t>
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>Capital Equipment — Self-Host Hardware (IN BASE CASE)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="21" t="inlineStr">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Hardware is mandatory from Y1 — EGPC requires in-house AI. Model A bears 25% of cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="B44" s="21" t="inlineStr">
+      <c r="B45" s="21" t="inlineStr">
         <is>
           <t>Configuration</t>
         </is>
       </c>
-      <c r="C44" s="21" t="inlineStr">
+      <c r="C45" s="21" t="inlineStr">
         <is>
           <t>Capital Cost (one-time)</t>
         </is>
       </c>
-      <c r="D44" s="21" t="inlineStr">
+      <c r="D45" s="21" t="inlineStr">
         <is>
           <t>Monthly Opex</t>
         </is>
       </c>
-      <c r="E44" s="21" t="inlineStr">
+      <c r="E45" s="21" t="inlineStr">
         <is>
           <t>Capacity</t>
         </is>
       </c>
-      <c r="F44" s="21" t="inlineStr">
+      <c r="F45" s="21" t="inlineStr">
         <is>
           <t>Break-even vs Cloud</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
-        </is>
-      </c>
-      <c r="B45" s="22" t="inlineStr">
-        <is>
-          <t>GLM 5.1 INT4, 8× A100 80GB, Dell XE9680</t>
-        </is>
-      </c>
-      <c r="C45" s="22" t="inlineStr">
-        <is>
-          <t>10.4M – 14.6M EGP</t>
-        </is>
-      </c>
-      <c r="D45" s="22" t="inlineStr">
-        <is>
-          <t>40-60K/mo</t>
-        </is>
-      </c>
-      <c r="E45" s="22" t="inlineStr">
-        <is>
-          <t>20-30 users</t>
-        </is>
-      </c>
-      <c r="F45" s="22" t="inlineStr">
-        <is>
-          <t>3-5 years</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>GLM 5.1 FP8, 8× H200 141GB, Dell XE9680</t>
+          <t>GLM 5.1 INT4, 8× A100 80GB, Dell XE9680</t>
         </is>
       </c>
       <c r="C46" s="22" t="inlineStr">
         <is>
-          <t>18.2M – 23.4M EGP</t>
+          <t>10.4M – 14.6M EGP</t>
         </is>
       </c>
       <c r="D46" s="22" t="inlineStr">
         <is>
-          <t>60-80K/mo</t>
+          <t>40-60K/mo</t>
         </is>
       </c>
       <c r="E46" s="22" t="inlineStr">
         <is>
-          <t>30-40 users</t>
+          <t>20-30 users</t>
         </is>
       </c>
       <c r="F46" s="22" t="inlineStr">
         <is>
-          <t>2-3 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="19" t="inlineStr">
+          <t>3-5 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>Tier 3 ⭐ SELECTED</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>Qwen3-32B, 4× A100 80GB, Dell R760xa</t>
+        </is>
+      </c>
+      <c r="C47" s="22" t="inlineStr">
+        <is>
+          <t>5.5M EGP (midpoint)</t>
+        </is>
+      </c>
+      <c r="D47" s="22" t="inlineStr">
+        <is>
+          <t>35K/mo (420K/yr)</t>
+        </is>
+      </c>
+      <c r="E47" s="22" t="inlineStr">
+        <is>
+          <t>80-100 users</t>
+        </is>
+      </c>
+      <c r="F47" s="22" t="inlineStr">
+        <is>
+          <t>N/A — self-host Y1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>Individual GPU Pricing (Egyptian Market, April 2026)</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="21" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="21" t="inlineStr">
         <is>
           <t>GPU</t>
         </is>
       </c>
-      <c r="B50" s="21" t="inlineStr">
+      <c r="B51" s="21" t="inlineStr">
         <is>
           <t>VRAM</t>
         </is>
       </c>
-      <c r="C50" s="21" t="inlineStr">
+      <c r="C51" s="21" t="inlineStr">
         <is>
           <t>USD Each</t>
         </is>
       </c>
-      <c r="D50" s="21" t="inlineStr">
+      <c r="D51" s="21" t="inlineStr">
         <is>
           <t>EGP Each (landed)</t>
         </is>
       </c>
-      <c r="E50" s="21" t="inlineStr">
+      <c r="E51" s="21" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="22" t="inlineStr">
-        <is>
-          <t>NVIDIA A100 80GB PCIe</t>
-        </is>
-      </c>
-      <c r="B51" s="22" t="inlineStr">
-        <is>
-          <t>80 GB</t>
-        </is>
-      </c>
-      <c r="C51" s="22" t="inlineStr">
-        <is>
-          <t>$15K-17K</t>
-        </is>
-      </c>
-      <c r="D51" s="22" t="inlineStr">
-        <is>
-          <t>~1,135,000</t>
-        </is>
-      </c>
-      <c r="E51" s="22" t="inlineStr">
-        <is>
-          <t>ServerBasket Egypt</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>NVIDIA H100 80GB SXM5</t>
+          <t>NVIDIA A100 80GB PCIe</t>
         </is>
       </c>
       <c r="B52" s="22" t="inlineStr">
@@ -1488,39 +1599,39 @@
       </c>
       <c r="C52" s="22" t="inlineStr">
         <is>
-          <t>$35K-40K</t>
+          <t>$15K-17K</t>
         </is>
       </c>
       <c r="D52" s="22" t="inlineStr">
         <is>
-          <t>~1.8M-2.1M</t>
+          <t>~1,135,000</t>
         </is>
       </c>
       <c r="E52" s="22" t="inlineStr">
         <is>
-          <t>OEM (in-server)</t>
+          <t>ServerBasket Egypt</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="22" t="inlineStr">
         <is>
-          <t>NVIDIA H200 141GB SXM5</t>
+          <t>NVIDIA H100 80GB SXM5</t>
         </is>
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>141 GB</t>
+          <t>80 GB</t>
         </is>
       </c>
       <c r="C53" s="22" t="inlineStr">
         <is>
-          <t>$35K-45K</t>
+          <t>$35K-40K</t>
         </is>
       </c>
       <c r="D53" s="22" t="inlineStr">
         <is>
-          <t>~1.8M-2.3M</t>
+          <t>~1.8M-2.1M</t>
         </is>
       </c>
       <c r="E53" s="22" t="inlineStr">
@@ -1532,92 +1643,112 @@
     <row r="54">
       <c r="A54" s="22" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 4090 24GB</t>
+          <t>NVIDIA H200 141GB SXM5</t>
         </is>
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>24 GB</t>
+          <t>141 GB</t>
         </is>
       </c>
       <c r="C54" s="22" t="inlineStr">
         <is>
-          <t>$2.1K-3K</t>
+          <t>$35K-45K</t>
         </is>
       </c>
       <c r="D54" s="22" t="inlineStr">
         <is>
-          <t>110K-155K</t>
+          <t>~1.8M-2.3M</t>
         </is>
       </c>
       <c r="E54" s="22" t="inlineStr">
         <is>
-          <t>Baraka / Compumarts</t>
+          <t>OEM (in-server)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="22" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 5090 32GB</t>
+          <t>NVIDIA RTX 4090 24GB</t>
         </is>
       </c>
       <c r="B55" s="22" t="inlineStr">
         <is>
-          <t>32 GB</t>
+          <t>24 GB</t>
         </is>
       </c>
       <c r="C55" s="22" t="inlineStr">
         <is>
-          <t>$3K-3.85K</t>
+          <t>$2.1K-3K</t>
         </is>
       </c>
       <c r="D55" s="22" t="inlineStr">
         <is>
-          <t>157K-200K</t>
+          <t>110K-155K</t>
         </is>
       </c>
       <c r="E55" s="22" t="inlineStr">
         <is>
-          <t>Compumarts / Baraka</t>
+          <t>Baraka / Compumarts</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="22" t="inlineStr">
         <is>
+          <t>NVIDIA RTX 5090 32GB</t>
+        </is>
+      </c>
+      <c r="B56" s="22" t="inlineStr">
+        <is>
+          <t>32 GB</t>
+        </is>
+      </c>
+      <c r="C56" s="22" t="inlineStr">
+        <is>
+          <t>$3K-3.85K</t>
+        </is>
+      </c>
+      <c r="D56" s="22" t="inlineStr">
+        <is>
+          <t>157K-200K</t>
+        </is>
+      </c>
+      <c r="E56" s="22" t="inlineStr">
+        <is>
+          <t>Compumarts / Baraka</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
           <t>Dell PowerEdge T560</t>
         </is>
       </c>
-      <c r="B56" s="22" t="inlineStr">
+      <c r="B57" s="22" t="inlineStr">
         <is>
           <t>server</t>
         </is>
       </c>
-      <c r="C56" s="22" t="inlineStr">
+      <c r="C57" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D56" s="22" t="inlineStr">
+      <c r="D57" s="22" t="inlineStr">
         <is>
           <t>~120K-180K</t>
         </is>
       </c>
-      <c r="E56" s="22" t="inlineStr">
+      <c r="E57" s="22" t="inlineStr">
         <is>
           <t>Elite Technology</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A28:E28"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1628,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1653,6 +1784,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ESE Model B — Corporate SaaS for EGPC Refineries (In-House AI — Mandatory)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1853,411 +1991,562 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Team (2-5 FTE lean)</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>1,010K</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>1,400K</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>2,100K</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>Lead AE, Solutions Eng, CS, Legal</t>
-        </is>
-      </c>
+          <t>Cost Structure (K EGP) — In-House AI, Hardware in Base Case</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="24" t="n"/>
+      <c r="E13" s="24" t="n"/>
+      <c r="F13" s="25" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Cloud AI (Claude API → RunPod)</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>120K</t>
+          <t>Y1</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>250K</t>
+          <t>Y2</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>350K</t>
+          <t>Y3</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Shared infra with Model A</t>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Certifications + Legal</t>
+          <t>Team (2-6 FTE lean)</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>175K</t>
+          <t>600K</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>80K</t>
+          <t>1,200K</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>80K</t>
+          <t>1,800K</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>No ISO 27001 Y1-Y3</t>
+          <t>Lead AE, Solutions Eng, CS, Legal, DevOps</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Marketing / EGPC BD</t>
+          <t>Hardware capex (75% of 5,500K)</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>4,125K</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>350K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>500K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Meetings, proposals, events</t>
+          <t>One-time, EGPC-mandated</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Travel &amp; On-site</t>
+          <t>Colocation + electricity (75% of 420K/yr)</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>120K</t>
+          <t>315K</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>315K</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>250K</t>
+          <t>315K</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Refinery visits, onboarding</t>
+          <t>Data center hosting for GPU server</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Misc / Contingency (10%)</t>
+          <t>DevOps/ML Engineer (75% of 360K/yr)</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>231K</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>260K</t>
+          <t>270K</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>405K</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr"/>
+          <t>270K</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Shared hire, Model A pays 25%</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Other (EC2, ITIDA, Legal, Ingestion)</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>1,856K</t>
+          <t>236K</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>2,520K</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>3,685K</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr"/>
+          <t>290K</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>EC2 36-60-90, ITIDA 50, Legal 150-50-50, Ingestion 0-100-150</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Marketing / EGPC BD</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>700K</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>500K</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>600K</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Relationship-driven, low spend</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Net Cash Flow</t>
+          <t>Customer Acquisition (travel, demos)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>100K</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>200K</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>300K</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Site visits, POC setup</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr"/>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Misc / Contingency</t>
+        </is>
+      </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Y1</t>
+          <t>100K</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Y2</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>3-Yr Cumulative</t>
-        </is>
-      </c>
+          <t>345K</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>6,311K</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2,855K</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3,920K</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Net Cash Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>75K</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>1,150K</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>2,250K</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>3,475K</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Costs</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>(1,856K)</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>(2,520K)</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>(3,685K)</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>(8,061K)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>(1,781K)</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>(1,370K)</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>(1,435K)</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>(4,586K)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>⚠ Model B is cash-negative through Y3. Strategic market-entry investment — real return in Y4+ (Model C at 10× ticket size).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>Capital Equipment Reference — Self-Host Scenario (for management Q&amp;A)</t>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>(6,311K)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>(2,855K)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>(3,920K)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>(13,086K)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>Model B stays cloud-first. Hardware purchase NOT in base case. See Model A sheet for full 3-tier breakdown.</t>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>(6,236K)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>(1,705K)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>(1,670K)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>(9,611K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>⚠ Model B is deeply cash-negative through Y3 due to mandatory Y1 hardware. Strategic market-entry investment.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="inlineStr">
-        <is>
-          <t>Configuration</t>
-        </is>
-      </c>
-      <c r="B33" s="21" t="inlineStr">
-        <is>
-          <t>Capital Cost</t>
-        </is>
-      </c>
-      <c r="C33" s="21" t="inlineStr">
-        <is>
-          <t>Monthly Opex</t>
-        </is>
-      </c>
-      <c r="D33" s="21" t="inlineStr">
-        <is>
-          <t>Break-even vs Cloud</t>
-        </is>
-      </c>
+      <c r="A33" s="21" t="n"/>
+      <c r="B33" s="21" t="n"/>
+      <c r="C33" s="21" t="n"/>
+      <c r="D33" s="21" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="22" t="inlineStr">
         <is>
-          <t>Tier 2 — 8× A100 80GB (GLM 5.1 INT4)</t>
-        </is>
-      </c>
-      <c r="B34" s="22" t="inlineStr">
-        <is>
-          <t>10.4M – 14.6M EGP</t>
-        </is>
-      </c>
-      <c r="C34" s="22" t="inlineStr">
-        <is>
-          <t>40-60K/mo</t>
-        </is>
-      </c>
-      <c r="D34" s="22" t="inlineStr">
-        <is>
-          <t>3-5 yr</t>
-        </is>
-      </c>
+          <t>Capital Equipment — In-House AI Hardware (IN BASE CASE)</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+      <c r="E34" s="26" t="n"/>
+      <c r="F34" s="27" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="22" t="inlineStr">
         <is>
-          <t>Tier 1 — 8× H200 141GB (GLM 5.1 FP8)</t>
-        </is>
-      </c>
-      <c r="B35" s="22" t="inlineStr">
-        <is>
-          <t>18.2M – 23.4M EGP</t>
-        </is>
-      </c>
-      <c r="C35" s="22" t="inlineStr">
-        <is>
-          <t>60-80K/mo</t>
-        </is>
-      </c>
-      <c r="D35" s="22" t="inlineStr">
-        <is>
-          <t>2-3 yr → buy wins</t>
+          <t>Hardware is mandatory from Y1 — EGPC requires in-house AI. Model B bears 75% of cost.</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Capital Cost</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Monthly Opex</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>Cloud vs. Buy Verdict for Model B</t>
+          <t>Tier 3 ⭐ SELECTED — Qwen3-32B, 4× A100 80GB, Dell R760xa</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>5.5M EGP (midpoint)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>35K/mo (420K/yr)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>80-100 users</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Y1 purchase</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="23" t="inlineStr">
         <is>
-          <t>Tier 3 (5.2-7.3M) ÷ 1.8M/yr TAM = 3-4 years just to recover hardware. Cloud API at ~1.2M/yr is cheaper through Y5+.</t>
+          <t>Tier 2 — GLM 5.1 INT4, 8× A100 80GB, Dell XE9680</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10.4M – 14.6M EGP</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>40-60K/mo</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>20-30 users</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Deferred to Model C</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="23" t="inlineStr">
         <is>
-          <t>Self-host only at Model C scale (8M+ per deal, customer pays hardware). Hardware will be 30-50% cheaper by Y4.</t>
+          <t>Tier 1 — GLM 5.1 FP8, 8× H200 141GB, Dell XE9680</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>18.2M – 23.4M EGP</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>60-80K/mo</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>30-40 users</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Deferred to Model C</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Hardware Decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tier 3 (5.5M midpoint) selected. Hardware is Y1 purchase — EGPC data sovereignty makes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>in-house AI mandatory regardless of TAM size. Hardware gets cheaper over time; upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>to Tier 2/1 deferred to Model C scale (8M+ per deal, customer-funded hardware).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A42:F42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2269,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2442,27 +2731,54 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>(3,961K)</t>
+          <t>(10,586K)</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>(1,350K)</t>
+          <t>(6,590K)</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>+2,040K</t>
+          <t>(8,720K)</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>(3,271K)</t>
+          <t>(25,896K)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
           <t>~Y3Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>(9,861K)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>(1,140K)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>+2,330K</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>(8,671K)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Y3Q4</t>
         </is>
       </c>
     </row>
@@ -2612,22 +2928,44 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>(4,150K)</t>
+          <t>(11,000K)</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>(3,600K)</t>
+          <t>(7,500K)</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>(2,500K)</t>
+          <t>(10,000K)</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>(10,250K)</t>
+          <t>(28,500K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>(10,650K)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>(4,600K)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>(4,000K)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>(19,250K)</t>
         </is>
       </c>
     </row>
@@ -2777,22 +3115,44 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>(3,650K)</t>
+          <t>(6,500K)</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>+3,500K</t>
+          <t>(6,000K)</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>+11,000K</t>
+          <t>(8,500K)</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>+10,850K</t>
+          <t>(21,000K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>(5,150K)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>+4,500K</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>+12,500K</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>+11,850K</t>
         </is>
       </c>
     </row>
@@ -2895,28 +3255,72 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
+          <t>9,250K</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>17,225K</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>32,850K</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>(19,250K)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>(8,671K)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>+11,850K</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>After Y3</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Y3Q4</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Y2Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>~22-28%</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>~65%</t>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>~50%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A28:E28"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2927,7 +3331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3047,17 +3451,17 @@
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>Model A Trial→Paid Conversion</t>
+          <t>Self-Host AI Cutover</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>8-12%</t>
+          <t>Y1Q2 (hardware delivery)</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>Industry SaaS benchmark for B2C freemium</t>
+          <t>EGPC requires in-house AI from Day 1</t>
         </is>
       </c>
     </row>
@@ -3098,34 +3502,34 @@
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>Shared Engineering Allocation</t>
+          <t>Data Sovereignty</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>20% Y1 → 10% Y3</t>
+          <t>All data on EPROM infrastructure in Egypt</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>Declining as Model A matures</t>
+          <t>Law 151/2020 + EGPC mandate compliant</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Model B as Standalone?</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>NO — cash-negative Y1-Y3</t>
+          <t>Self-host Qwen3-32B on 4× A100 from Y1</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>Strategic investment for Model C</t>
+          <t>EGPC mandate — no cloud AI alternative</t>
         </is>
       </c>
     </row>
@@ -3173,12 +3577,17 @@
     <row r="18">
       <c r="A18" s="23" t="inlineStr">
         <is>
-          <t>Tier 3 — Qwen3-32B 4× A100 80GB</t>
+          <t>Tier 3 ⭐ SELECTED — Qwen3-32B 4× A100 80GB</t>
         </is>
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>5.2M – 7.3M EGP one-time</t>
+          <t>5.5M EGP one-time (midpoint)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>In base case, mandatory Y1 purchase</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3635,12 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>Only at Model C scale (8M+ per deal, customer-funded)</t>
+          <t>Immediate — EGPC compliance (Y1Q1 order)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Not optional. Entry ticket to EGPC market.</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3652,12 @@
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>-40% hardware cost per 2 years (same capability gets cheaper)</t>
+          <t>-40% hardware cost per 2 years</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Upgrade to Tier 2/1 only when Model C justifies</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3669,63 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>Y3Q4 Board review — not before</t>
+          <t>Y1Q1 — Immediate purchase (not deferred)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EGPC data sovereignty non-negotiable</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Hardware Attribution</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Model A 25%, Model B 75%</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Model B EGPC requirement drives purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Colocation Cost</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>420K EGP/yr total (35K/mo)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Shared 25/75 between Model A/B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DevOps/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>360K EGP/yr (30K/mo)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Hired Y1Q3 (half-year Y1). Shared 25/75</t>
         </is>
       </c>
     </row>
